--- a/exports/MIDCPNIFTY_full_report.xlsx
+++ b/exports/MIDCPNIFTY_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q83"/>
+  <dimension ref="A1:U83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>7</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44603.55208333334</v>
+        <v>44606.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>7352.6</v>
+        <v>7162.4</v>
       </c>
       <c r="I2" t="n">
         <v>7289.783574164499</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.47</v>
+        <v>-4.99</v>
       </c>
       <c r="L2" t="n">
-        <v>3.09</v>
+        <v>5.94</v>
       </c>
       <c r="M2" t="n">
-        <v>0.43</v>
+        <v>2.05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.18</v>
+        <v>4.4</v>
       </c>
       <c r="O2" t="n">
         <v>1.34</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>4.75</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44635.55208333334</v>
+        <v>44636.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>6920.4</v>
+        <v>7055.75</v>
       </c>
       <c r="I3" t="n">
         <v>6955.239102932909</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K3" t="n">
-        <v>3.38</v>
+        <v>1.49</v>
       </c>
       <c r="L3" t="n">
         <v>3.17</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>5.14</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44664.55208333334</v>
+        <v>44669.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>7491.65</v>
+        <v>7336.55</v>
       </c>
       <c r="I4" t="n">
         <v>7470.427879493412</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K4" t="n">
-        <v>6.18</v>
+        <v>3.98</v>
       </c>
       <c r="L4" t="n">
         <v>0.72</v>
       </c>
       <c r="M4" t="n">
-        <v>0.14</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
         <v>1.73</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>3.84</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44708.55208333334</v>
+        <v>44711.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>6663.2</v>
+        <v>6796.3</v>
       </c>
       <c r="I5" t="n">
         <v>6781.330692908642</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K5" t="n">
-        <v>9.18</v>
+        <v>7.36</v>
       </c>
       <c r="L5" t="n">
         <v>1.95</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,25 +833,25 @@
         <v>5.15</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44721.55208333334</v>
+        <v>44722.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>6701.95</v>
+        <v>6634.9</v>
       </c>
       <c r="I6" t="n">
         <v>6635.705974094264</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.39</v>
+        <v>-2.37</v>
       </c>
       <c r="L6" t="n">
         <v>2.92</v>
       </c>
       <c r="M6" t="n">
-        <v>0.37</v>
+        <v>0.9</v>
       </c>
       <c r="N6" t="n">
         <v>1.58</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,25 +902,25 @@
         <v>3.53</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44736.55208333334</v>
+        <v>44739.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>6361.25</v>
+        <v>6466.4</v>
       </c>
       <c r="I7" t="n">
         <v>6396.19787846082</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K7" t="n">
-        <v>4.12</v>
+        <v>2.54</v>
       </c>
       <c r="L7" t="n">
         <v>0.32</v>
       </c>
       <c r="M7" t="n">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="N7" t="n">
         <v>2.52</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>4.32</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44795.38541666666</v>
+        <v>44795.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>7295.5</v>
+        <v>7244.05</v>
       </c>
       <c r="I8" t="n">
         <v>7290.238413558637</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>56</v>
+        <v>56.16666666666666</v>
       </c>
       <c r="K8" t="n">
-        <v>12.82</v>
+        <v>12.03</v>
       </c>
       <c r="L8" t="n">
         <v>2.96</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>3.26</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44809.55208333334</v>
+        <v>44810.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>7464.85</v>
+        <v>7491.15</v>
       </c>
       <c r="I9" t="n">
         <v>7478.682846677761</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.05</v>
+        <v>-3.41</v>
       </c>
       <c r="L9" t="n">
-        <v>3.53</v>
+        <v>3.79</v>
       </c>
       <c r="M9" t="n">
         <v>0.67</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>2.73</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44819.55208333334</v>
+        <v>44820.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>7641.15</v>
+        <v>7455.1</v>
       </c>
       <c r="I10" t="n">
         <v>7525.408093559227</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>-0.48</v>
       </c>
       <c r="L10" t="n">
         <v>0.55</v>
@@ -1011,7 +1130,7 @@
         <v>1.38</v>
       </c>
       <c r="N10" t="n">
-        <v>0.71</v>
+        <v>3.02</v>
       </c>
       <c r="O10" t="n">
         <v>0.21</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>4.29</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>7319.25</v>
+        <v>7447.5</v>
       </c>
       <c r="I11" t="n">
         <v>7361.839498870778</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>1.82</v>
+        <v>0.1</v>
       </c>
       <c r="L11" t="n">
         <v>2.72</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>4.71</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44876.55208333334</v>
+        <v>44879.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>7327.8</v>
+        <v>7313.75</v>
       </c>
       <c r="I12" t="n">
         <v>7320.338165995858</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.61</v>
+        <v>-1.8</v>
       </c>
       <c r="L12" t="n">
         <v>4.44</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>2.57</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44890.38541666666</v>
+        <v>44890.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>7328.85</v>
+        <v>7334.3</v>
       </c>
       <c r="I13" t="n">
         <v>7329.23382181036</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.21</v>
+        <v>-0.28</v>
       </c>
       <c r="L13" t="n">
-        <v>0.35</v>
+        <v>0.47</v>
       </c>
       <c r="M13" t="n">
         <v>0.53</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>1.8</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44911.38541666666</v>
+        <v>44911.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>7350.85</v>
+        <v>7296.6</v>
       </c>
       <c r="I14" t="n">
         <v>7340.33564392677</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K14" t="n">
-        <v>0.23</v>
+        <v>-0.51</v>
       </c>
       <c r="L14" t="n">
         <v>0.61</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>2.76</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44925.55208333334</v>
+        <v>44928.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>7187.05</v>
+        <v>7216.65</v>
       </c>
       <c r="I15" t="n">
         <v>7216.320412988274</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>14</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="L15" t="n">
         <v>1.16</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>3.23</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44942.38541666666</v>
+        <v>44942.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>7022.55</v>
+        <v>6999.6</v>
       </c>
       <c r="I16" t="n">
         <v>7021.131969576247</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.69</v>
+        <v>-3.01</v>
       </c>
       <c r="L16" t="n">
-        <v>2.98</v>
+        <v>3.11</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>2.59</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44956.55208333334</v>
+        <v>44958.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>6830.3</v>
+        <v>7088.45</v>
       </c>
       <c r="I17" t="n">
         <v>6991.86116900965</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>14</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>2.42</v>
+        <v>-1.27</v>
       </c>
       <c r="L17" t="n">
-        <v>0.93</v>
+        <v>1.6</v>
       </c>
       <c r="M17" t="n">
-        <v>0.46</v>
+        <v>2.48</v>
       </c>
       <c r="N17" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="O17" t="n">
         <v>-0.76</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,25 +1661,25 @@
         <v>4.42</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44978.55208333334</v>
+        <v>44979.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>6959.3</v>
+        <v>6883.1</v>
       </c>
       <c r="I18" t="n">
         <v>6894.686009878472</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.82</v>
+        <v>-2.9</v>
       </c>
       <c r="L18" t="n">
         <v>3.82</v>
       </c>
       <c r="M18" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="N18" t="n">
         <v>1.47</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>2.95</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44988.55208333334</v>
+        <v>44991.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>6915.4</v>
+        <v>6972.35</v>
       </c>
       <c r="I19" t="n">
         <v>6925.012506298206</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.47</v>
+        <v>-1.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.03</v>
+        <v>1.52</v>
       </c>
       <c r="M19" t="n">
         <v>0.59</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>2.43</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44995.55208333334</v>
+        <v>44998.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>6903.05</v>
+        <v>6821.3</v>
       </c>
       <c r="I20" t="n">
         <v>6852.927955592062</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.99</v>
+        <v>-2.17</v>
       </c>
       <c r="L20" t="n">
-        <v>2.03</v>
+        <v>2.34</v>
       </c>
       <c r="M20" t="n">
         <v>0.58</v>
       </c>
       <c r="N20" t="n">
-        <v>0.88</v>
+        <v>1.97</v>
       </c>
       <c r="O20" t="n">
         <v>0.53</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>3.29</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45014.55208333334</v>
+        <v>45016.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>6731.8</v>
+        <v>6822.85</v>
       </c>
       <c r="I21" t="n">
         <v>6784.036068589096</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K21" t="n">
-        <v>1.31</v>
+        <v>-0.02</v>
       </c>
       <c r="L21" t="n">
         <v>1.37</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>3.13</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45099.55208333334</v>
+        <v>45100.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>8083.1</v>
+        <v>8014.35</v>
       </c>
       <c r="I22" t="n">
         <v>8049.229770027707</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>83.16666666666667</v>
+        <v>84</v>
       </c>
       <c r="K22" t="n">
-        <v>18.47</v>
+        <v>17.46</v>
       </c>
       <c r="L22" t="n">
         <v>0.9</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>2.52</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45105.55208333334</v>
+        <v>45107.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>8167.6</v>
+        <v>8224</v>
       </c>
       <c r="I23" t="n">
         <v>8188.511613711706</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.91</v>
+        <v>-2.62</v>
       </c>
       <c r="L23" t="n">
-        <v>1.99</v>
+        <v>2.82</v>
       </c>
       <c r="M23" t="n">
         <v>0.57</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>2.38</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45180.55208333334</v>
+        <v>45181.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>9201.450000000001</v>
+        <v>8975.35</v>
       </c>
       <c r="I24" t="n">
         <v>9060.9410963585</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>73.16666666666667</v>
+        <v>74</v>
       </c>
       <c r="K24" t="n">
-        <v>11.89</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="L24" t="n">
         <v>0.63</v>
@@ -1809,7 +2096,7 @@
         <v>0.42</v>
       </c>
       <c r="N24" t="n">
-        <v>1.22</v>
+        <v>2.66</v>
       </c>
       <c r="O24" t="n">
         <v>0.74</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>3.7</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45184.38541666666</v>
+        <v>45184.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>9150.85</v>
+        <v>9174.049999999999</v>
       </c>
       <c r="I25" t="n">
         <v>9166.417015754654</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.96</v>
+        <v>-2.21</v>
       </c>
       <c r="L25" t="n">
         <v>2.96</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,25 +2213,25 @@
         <v>2.34</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45202.55208333334</v>
+        <v>45203.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>9106.299999999999</v>
+        <v>8952.549999999999</v>
       </c>
       <c r="I26" t="n">
         <v>8979.369467869536</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.74</v>
+        <v>-2.41</v>
       </c>
       <c r="L26" t="n">
-        <v>2.16</v>
+        <v>2.63</v>
       </c>
       <c r="M26" t="n">
-        <v>0.25</v>
+        <v>0.32</v>
       </c>
       <c r="N26" t="n">
         <v>1.95</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>3.3</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45233.55208333334</v>
+        <v>45236.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>8893.5</v>
+        <v>8964.549999999999</v>
       </c>
       <c r="I27" t="n">
         <v>8899.709790070041</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K27" t="n">
-        <v>0.66</v>
+        <v>-0.13</v>
       </c>
       <c r="L27" t="n">
         <v>3.02</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>2.52</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>10328.15</v>
+        <v>9992</v>
       </c>
       <c r="I28" t="n">
         <v>10129.06439775142</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>44</v>
+        <v>44.16666666666666</v>
       </c>
       <c r="K28" t="n">
-        <v>15.21</v>
+        <v>11.46</v>
       </c>
       <c r="L28" t="n">
         <v>0.45</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>4.81</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45287.55208333334</v>
+        <v>45288.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>10295.5</v>
+        <v>10357.25</v>
       </c>
       <c r="I29" t="n">
         <v>10348.16758782135</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.04</v>
+        <v>-3.66</v>
       </c>
       <c r="L29" t="n">
         <v>3.77</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>3.08</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45314.38541666666</v>
+        <v>45314.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>10435.85</v>
+        <v>10356.35</v>
       </c>
       <c r="I30" t="n">
         <v>10391.7226293305</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>0.76</v>
+        <v>-0.01</v>
       </c>
       <c r="L30" t="n">
         <v>1.74</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>3.77</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45324.55208333334</v>
+        <v>45327.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>10728.05</v>
+        <v>10780.3</v>
       </c>
       <c r="I31" t="n">
         <v>10747.22599287503</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>10</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.59</v>
+        <v>-4.09</v>
       </c>
       <c r="L31" t="n">
-        <v>4.23</v>
+        <v>4.5</v>
       </c>
       <c r="M31" t="n">
         <v>0.78</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>3.97</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45349.55208333334</v>
+        <v>45350.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>10996.65</v>
+        <v>10754.6</v>
       </c>
       <c r="I32" t="n">
         <v>10769.67463469075</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K32" t="n">
-        <v>2.01</v>
+        <v>-0.24</v>
       </c>
       <c r="L32" t="n">
         <v>2.24</v>
@@ -2265,7 +2648,7 @@
         <v>0.85</v>
       </c>
       <c r="N32" t="n">
-        <v>1.24</v>
+        <v>2.49</v>
       </c>
       <c r="O32" t="n">
         <v>0.13</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>4.94</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45379.55208333334</v>
+        <v>45383.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>10533.95</v>
+        <v>10641.85</v>
       </c>
       <c r="I33" t="n">
         <v>10587.91698276078</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K33" t="n">
-        <v>2.05</v>
+        <v>1.05</v>
       </c>
       <c r="L33" t="n">
         <v>2.54</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>3.11</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45400.55208333334</v>
+        <v>45401.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>10778.7</v>
+        <v>10677.1</v>
       </c>
       <c r="I34" t="n">
         <v>10729.88998235361</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K34" t="n">
-        <v>1.29</v>
+        <v>0.33</v>
       </c>
       <c r="L34" t="n">
-        <v>0.46</v>
+        <v>1.03</v>
       </c>
       <c r="M34" t="n">
         <v>1.18</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>2.76</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45407.55208333334</v>
+        <v>45408.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>10876.25</v>
+        <v>10988</v>
       </c>
       <c r="I35" t="n">
         <v>10972.19607725804</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K35" t="n">
-        <v>-1.87</v>
+        <v>-2.91</v>
       </c>
       <c r="L35" t="n">
-        <v>2.02</v>
+        <v>3.02</v>
       </c>
       <c r="M35" t="n">
         <v>0.88</v>
       </c>
       <c r="N35" t="n">
-        <v>0.71</v>
+        <v>0.98</v>
       </c>
       <c r="O35" t="n">
         <v>-0.97</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>2.67</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>11043.7</v>
+        <v>10764.75</v>
       </c>
       <c r="I36" t="n">
         <v>10910.8494127835</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K36" t="n">
-        <v>0.51</v>
+        <v>-2.03</v>
       </c>
       <c r="L36" t="n">
-        <v>0.87</v>
+        <v>2.12</v>
       </c>
       <c r="M36" t="n">
         <v>0.01</v>
       </c>
       <c r="N36" t="n">
-        <v>0.67</v>
+        <v>1.82</v>
       </c>
       <c r="O36" t="n">
         <v>0.98</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>4.31</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45426.38541666666</v>
+        <v>45426.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>11108.15</v>
+        <v>11128.1</v>
       </c>
       <c r="I37" t="n">
         <v>11119.73328252093</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.19</v>
+        <v>-3.38</v>
       </c>
       <c r="L37" t="n">
-        <v>3.3</v>
+        <v>3.59</v>
       </c>
       <c r="M37" t="n">
         <v>0.31</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>3.32</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45442.38541666666</v>
+        <v>45442.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>11399</v>
+        <v>11353.45</v>
       </c>
       <c r="I38" t="n">
         <v>11382.22069836131</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>15.83333333333333</v>
+        <v>16</v>
       </c>
       <c r="K38" t="n">
-        <v>2.43</v>
+        <v>2.03</v>
       </c>
       <c r="L38" t="n">
         <v>0.22</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>3.04</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45443.55208333334</v>
+        <v>45446.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>11374.6</v>
+        <v>11708.6</v>
       </c>
       <c r="I39" t="n">
         <v>11677.7800220609</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.19</v>
+        <v>-3.13</v>
       </c>
       <c r="L39" t="n">
-        <v>0.54</v>
+        <v>3.55</v>
       </c>
       <c r="M39" t="n">
-        <v>0.33</v>
+        <v>3.36</v>
       </c>
       <c r="N39" t="n">
-        <v>0.19</v>
+        <v>3.41</v>
       </c>
       <c r="O39" t="n">
         <v>-1.44</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>3.73</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>11762.8</v>
+        <v>10920.25</v>
       </c>
       <c r="I40" t="n">
         <v>11327.05168213067</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>0.46</v>
+        <v>-6.73</v>
       </c>
       <c r="L40" t="n">
-        <v>0.91</v>
+        <v>10.71</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>7.48</v>
       </c>
       <c r="O40" t="n">
         <v>3.41</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>8.41</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45449.55208333334</v>
+        <v>45450.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>11609.6</v>
+        <v>11703.55</v>
       </c>
       <c r="I41" t="n">
         <v>11675.19438747416</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K41" t="n">
-        <v>-6.31</v>
+        <v>-7.17</v>
       </c>
       <c r="L41" t="n">
-        <v>7.4</v>
+        <v>7.47</v>
       </c>
       <c r="M41" t="n">
         <v>1.15</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>6.62</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45491.55208333334</v>
+        <v>45492.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>12470.45</v>
+        <v>12238.55</v>
       </c>
       <c r="I42" t="n">
         <v>12304.78821133609</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>41.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K42" t="n">
-        <v>6.55</v>
+        <v>4.57</v>
       </c>
       <c r="L42" t="n">
         <v>1.07</v>
@@ -2835,7 +3338,7 @@
         <v>0.36</v>
       </c>
       <c r="N42" t="n">
-        <v>0.95</v>
+        <v>2.38</v>
       </c>
       <c r="O42" t="n">
         <v>1.2</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>3.39</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45498.55208333334</v>
+        <v>45499.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>12426.25</v>
+        <v>12662.2</v>
       </c>
       <c r="I43" t="n">
         <v>12532.34469683816</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.53</v>
+        <v>-3.46</v>
       </c>
       <c r="L43" t="n">
-        <v>2.13</v>
+        <v>3.57</v>
       </c>
       <c r="M43" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="N43" t="n">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="O43" t="n">
         <v>-2.38</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>4.82</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>12598.7</v>
+        <v>12238.8</v>
       </c>
       <c r="I44" t="n">
         <v>12576.1678103456</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.5</v>
+        <v>-3.34</v>
       </c>
       <c r="L44" t="n">
-        <v>1.99</v>
+        <v>3.71</v>
       </c>
       <c r="M44" t="n">
-        <v>0.99</v>
+        <v>2.28</v>
       </c>
       <c r="N44" t="n">
-        <v>2.01</v>
+        <v>2.54</v>
       </c>
       <c r="O44" t="n">
         <v>2.12</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>4.48</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45523.38541666666</v>
+        <v>45523.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>12692.75</v>
+        <v>12762.05</v>
       </c>
       <c r="I45" t="n">
         <v>12725.72897635212</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K45" t="n">
-        <v>-3.71</v>
+        <v>-4.28</v>
       </c>
       <c r="L45" t="n">
         <v>4.7</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>3.33</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45541.55208333334</v>
+        <v>45544.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>13068.4</v>
+        <v>13007.05</v>
       </c>
       <c r="I46" t="n">
         <v>13057.81764673174</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>18</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K46" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="L46" t="n">
         <v>0.87</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>2.04</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45547.38541666666</v>
+        <v>45547.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>13221.1</v>
+        <v>13265.7</v>
       </c>
       <c r="I47" t="n">
         <v>13261.49388947931</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.65</v>
+        <v>-1.99</v>
       </c>
       <c r="L47" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="M47" t="n">
         <v>0.59</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>2.3</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45553.55208333334</v>
+        <v>45554.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>13120.9</v>
+        <v>12942.3</v>
       </c>
       <c r="I48" t="n">
         <v>13085.58202275904</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K48" t="n">
-        <v>-1.09</v>
+        <v>-2.44</v>
       </c>
       <c r="L48" t="n">
-        <v>1.63</v>
+        <v>2.9</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>4</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45580.38541666666</v>
+        <v>45580.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>13088.55</v>
+        <v>13150</v>
       </c>
       <c r="I49" t="n">
         <v>13122.59093735099</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.13</v>
+        <v>-1.6</v>
       </c>
       <c r="L49" t="n">
         <v>3.23</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>3.11</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45586.38541666666</v>
+        <v>45586.55208333334</v>
       </c>
       <c r="H50" t="n">
-        <v>12867.25</v>
+        <v>12683.1</v>
       </c>
       <c r="I50" t="n">
         <v>12811.88344624732</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.15</v>
+        <v>-3.55</v>
       </c>
       <c r="L50" t="n">
-        <v>2.59</v>
+        <v>3.8</v>
       </c>
       <c r="M50" t="n">
         <v>0.43</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,25 +3938,25 @@
         <v>4.33</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45618.55208333334</v>
+        <v>45621.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>12309.85</v>
+        <v>12566.25</v>
       </c>
       <c r="I51" t="n">
         <v>12460.31768109454</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>32</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K51" t="n">
-        <v>2.94</v>
+        <v>0.92</v>
       </c>
       <c r="L51" t="n">
         <v>1.71</v>
       </c>
       <c r="M51" t="n">
-        <v>0.6</v>
+        <v>1.54</v>
       </c>
       <c r="N51" t="n">
         <v>2.47</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>3.8</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45645.55208333334</v>
+        <v>45646.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>13032.4</v>
+        <v>12835.45</v>
       </c>
       <c r="I52" t="n">
         <v>12959.17386143633</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K52" t="n">
-        <v>3.71</v>
+        <v>2.14</v>
       </c>
       <c r="L52" t="n">
         <v>0.86</v>
@@ -3405,7 +4028,7 @@
         <v>1.6</v>
       </c>
       <c r="N52" t="n">
-        <v>0.93</v>
+        <v>2.59</v>
       </c>
       <c r="O52" t="n">
         <v>2.28</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>3.46</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45659.38541666666</v>
+        <v>45659.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>12989.35</v>
+        <v>13089</v>
       </c>
       <c r="I53" t="n">
         <v>13080.51871898666</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K53" t="n">
-        <v>-1.2</v>
+        <v>-1.98</v>
       </c>
       <c r="L53" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="M53" t="n">
         <v>0.4</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>3.04</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45663.38541666666</v>
+        <v>45663.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>12763.55</v>
+        <v>12691.05</v>
       </c>
       <c r="I54" t="n">
         <v>12691.55430107261</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>3.833333333333333</v>
+        <v>4</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.49</v>
+        <v>-3.04</v>
       </c>
       <c r="L54" t="n">
-        <v>2.9</v>
+        <v>3.31</v>
       </c>
       <c r="M54" t="n">
         <v>0.01</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>3.37</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45721.55208333334</v>
+        <v>45722.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>11171.65</v>
+        <v>11228.35</v>
       </c>
       <c r="I55" t="n">
         <v>11201.22376743861</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>58</v>
+        <v>58.83333333333334</v>
       </c>
       <c r="K55" t="n">
-        <v>11.97</v>
+        <v>11.53</v>
       </c>
       <c r="L55" t="n">
         <v>1.38</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>4.1</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45750.55208333334</v>
+        <v>45751.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>11513.15</v>
+        <v>11212.3</v>
       </c>
       <c r="I56" t="n">
         <v>11319.28997836188</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K56" t="n">
-        <v>2.54</v>
+        <v>-0.14</v>
       </c>
       <c r="L56" t="n">
         <v>4.02</v>
@@ -3633,7 +4304,7 @@
         <v>0.57</v>
       </c>
       <c r="N56" t="n">
-        <v>1.75</v>
+        <v>2.66</v>
       </c>
       <c r="O56" t="n">
         <v>0.04</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>5.32</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45756.55208333334</v>
+        <v>45758.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>11003.9</v>
+        <v>11273.85</v>
       </c>
       <c r="I57" t="n">
         <v>11254.07880044172</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K57" t="n">
-        <v>1.86</v>
+        <v>-0.55</v>
       </c>
       <c r="L57" t="n">
         <v>2.57</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>6.3</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45820.38541666666</v>
+        <v>45820.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>13165.95</v>
+        <v>13014.35</v>
       </c>
       <c r="I58" t="n">
         <v>13037.97546173476</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>62</v>
+        <v>62.16666666666666</v>
       </c>
       <c r="K58" t="n">
-        <v>16.78</v>
+        <v>15.44</v>
       </c>
       <c r="L58" t="n">
         <v>1.3</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3783,25 +4490,25 @@
         <v>2.96</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45831.55208333334</v>
+        <v>45832.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>13024</v>
+        <v>13217.65</v>
       </c>
       <c r="I59" t="n">
         <v>13113.47641909464</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.56</v>
       </c>
       <c r="L59" t="n">
-        <v>1.26</v>
+        <v>1.71</v>
       </c>
       <c r="M59" t="n">
-        <v>0.26</v>
+        <v>1.41</v>
       </c>
       <c r="N59" t="n">
         <v>1.96</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>3.34</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45848.55208333334</v>
+        <v>45849.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>13204.7</v>
+        <v>13041.8</v>
       </c>
       <c r="I60" t="n">
         <v>13172.09059668274</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.1</v>
+        <v>-1.33</v>
       </c>
       <c r="L60" t="n">
-        <v>0.71</v>
+        <v>1.54</v>
       </c>
       <c r="M60" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="N60" t="n">
-        <v>0.63</v>
+        <v>1.47</v>
       </c>
       <c r="O60" t="n">
         <v>0.93</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>2.97</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45853.38541666666</v>
+        <v>45853.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>13304.55</v>
+        <v>13346.15</v>
       </c>
       <c r="I61" t="n">
         <v>13334.84397250654</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K61" t="n">
-        <v>-2.01</v>
+        <v>-2.33</v>
       </c>
       <c r="L61" t="n">
-        <v>2.05</v>
+        <v>2.42</v>
       </c>
       <c r="M61" t="n">
         <v>0.48</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,25 +4697,25 @@
         <v>2.57</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45862.55208333334</v>
+        <v>45863.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>13100.4</v>
+        <v>12942.3</v>
       </c>
       <c r="I62" t="n">
         <v>13043.29043908215</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K62" t="n">
-        <v>-1.84</v>
+        <v>-3.03</v>
       </c>
       <c r="L62" t="n">
-        <v>2.04</v>
+        <v>3.21</v>
       </c>
       <c r="M62" t="n">
-        <v>0.05</v>
+        <v>0.22</v>
       </c>
       <c r="N62" t="n">
         <v>1.31</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>3.15</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45888.55208333334</v>
+        <v>45889.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>12917.95</v>
+        <v>13009.3</v>
       </c>
       <c r="I63" t="n">
         <v>12951.53292087554</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K63" t="n">
-        <v>0.19</v>
+        <v>-0.52</v>
       </c>
       <c r="L63" t="n">
         <v>1.3</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>3.35</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45895.38541666666</v>
+        <v>45895.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>12743.75</v>
+        <v>12674.15</v>
       </c>
       <c r="I64" t="n">
         <v>12689.1754221644</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.04</v>
+        <v>-2.58</v>
       </c>
       <c r="L64" t="n">
-        <v>2.16</v>
+        <v>2.72</v>
       </c>
       <c r="M64" t="n">
         <v>0.49</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>2.79</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45905.55208333334</v>
+        <v>45908.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>12786.35</v>
+        <v>12908.15</v>
       </c>
       <c r="I65" t="n">
         <v>12836.13209736953</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>10</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.89</v>
+        <v>-1.85</v>
       </c>
       <c r="L65" t="n">
         <v>2.17</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>3.15</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45923.55208333334</v>
+        <v>45924.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>13074.2</v>
+        <v>12963.8</v>
       </c>
       <c r="I66" t="n">
         <v>13034.53613201261</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K66" t="n">
-        <v>1.29</v>
+        <v>0.43</v>
       </c>
       <c r="L66" t="n">
         <v>0.92</v>
@@ -4203,7 +4994,7 @@
         <v>0.63</v>
       </c>
       <c r="N66" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="O66" t="n">
         <v>0.54</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>2.29</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45936.38541666666</v>
+        <v>45936.55208333334</v>
       </c>
       <c r="H67" t="n">
-        <v>12862.35</v>
+        <v>12942.65</v>
       </c>
       <c r="I67" t="n">
         <v>12874.21863155608</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K67" t="n">
-        <v>0.78</v>
+        <v>0.16</v>
       </c>
       <c r="L67" t="n">
         <v>0.82</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>2.45</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45985.38541666666</v>
+        <v>45985.55208333334</v>
       </c>
       <c r="H68" t="n">
-        <v>13819.2</v>
+        <v>13727.3</v>
       </c>
       <c r="I68" t="n">
         <v>13775.86752470258</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>48.83333333333334</v>
+        <v>49</v>
       </c>
       <c r="K68" t="n">
-        <v>6.77</v>
+        <v>6.06</v>
       </c>
       <c r="L68" t="n">
         <v>0.64</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>2.43</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45988.38541666666</v>
+        <v>45988.55208333334</v>
       </c>
       <c r="H69" t="n">
-        <v>14016.8</v>
+        <v>14068.5</v>
       </c>
       <c r="I69" t="n">
         <v>14051.40666805454</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>2.833333333333333</v>
+        <v>3</v>
       </c>
       <c r="K69" t="n">
-        <v>-2.11</v>
+        <v>-2.49</v>
       </c>
       <c r="L69" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="M69" t="n">
         <v>0.27</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>2.2</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45996.55208333334</v>
+        <v>45999.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>13993.2</v>
+        <v>13796.2</v>
       </c>
       <c r="I70" t="n">
         <v>13817.87863458317</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>8</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.54</v>
+        <v>-1.94</v>
       </c>
       <c r="L70" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="M70" t="n">
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>0.96</v>
+        <v>1.73</v>
       </c>
       <c r="O70" t="n">
         <v>0.39</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>3.31</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46023.55208333334</v>
+        <v>46024.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>13847.4</v>
+        <v>13968.35</v>
       </c>
       <c r="I71" t="n">
         <v>13893.39478091271</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K71" t="n">
-        <v>-0.37</v>
+        <v>-1.25</v>
       </c>
       <c r="L71" t="n">
         <v>1.86</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>2.51</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46030.55208333334</v>
+        <v>46031.38541666666</v>
       </c>
       <c r="H72" t="n">
-        <v>13755.25</v>
+        <v>13709.15</v>
       </c>
       <c r="I72" t="n">
         <v>13748.88048327607</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K72" t="n">
-        <v>-1.53</v>
+        <v>-1.86</v>
       </c>
       <c r="L72" t="n">
-        <v>1.64</v>
+        <v>2.17</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>3.02</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>13268.3</v>
+        <v>13656.65</v>
       </c>
       <c r="I73" t="n">
         <v>13543.99327385497</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K73" t="n">
-        <v>3.22</v>
+        <v>0.38</v>
       </c>
       <c r="L73" t="n">
-        <v>0.99</v>
+        <v>1.89</v>
       </c>
       <c r="M73" t="n">
-        <v>0.99</v>
+        <v>4.44</v>
       </c>
       <c r="N73" t="n">
-        <v>1.92</v>
+        <v>2.91</v>
       </c>
       <c r="O73" t="n">
         <v>-0.52</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,22 +5525,22 @@
         <v>4.91</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46072.38541666666</v>
+        <v>46072.55208333334</v>
       </c>
       <c r="H74" t="n">
-        <v>13593.7</v>
+        <v>13410.3</v>
       </c>
       <c r="I74" t="n">
         <v>13515.54980777129</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K74" t="n">
-        <v>-0.46</v>
+        <v>-1.8</v>
       </c>
       <c r="L74" t="n">
-        <v>1.56</v>
+        <v>1.88</v>
       </c>
       <c r="M74" t="n">
         <v>0.92</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,28 +5594,28 @@
         <v>3.66</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H75" t="n">
-        <v>12611.4</v>
+        <v>13206.95</v>
       </c>
       <c r="I75" t="n">
         <v>12842.07410956255</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>47</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="K75" t="n">
-        <v>5.96</v>
+        <v>1.52</v>
       </c>
       <c r="L75" t="n">
         <v>2.09</v>
       </c>
       <c r="M75" t="n">
-        <v>2.84</v>
+        <v>3.6</v>
       </c>
       <c r="N75" t="n">
-        <v>3</v>
+        <v>4.99</v>
       </c>
       <c r="O75" t="n">
         <v>-2.3</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>6.51</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46154.38541666666</v>
+        <v>46154.55208333334</v>
       </c>
       <c r="H76" t="n">
-        <v>14140.75</v>
+        <v>13994.9</v>
       </c>
       <c r="I76" t="n">
         <v>14100.35311118948</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>34</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="K76" t="n">
-        <v>7.07</v>
+        <v>5.97</v>
       </c>
       <c r="L76" t="n">
         <v>1.42</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4809,25 +5732,25 @@
         <v>3.83</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46164.55208333334</v>
+        <v>46167.38541666666</v>
       </c>
       <c r="H77" t="n">
-        <v>14397.15</v>
+        <v>14516.6</v>
       </c>
       <c r="I77" t="n">
         <v>14512.41763795881</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>10</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K77" t="n">
-        <v>-2.87</v>
+        <v>-3.73</v>
       </c>
       <c r="L77" t="n">
-        <v>3.77</v>
+        <v>3.97</v>
       </c>
       <c r="M77" t="n">
-        <v>0.68</v>
+        <v>0.92</v>
       </c>
       <c r="N77" t="n">
         <v>1.39</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S77" t="b">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -4866,28 +5801,28 @@
         <v>2.86</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46171.55208333334</v>
+        <v>46174.38541666666</v>
       </c>
       <c r="H78" t="n">
-        <v>14520.7</v>
+        <v>14290.95</v>
       </c>
       <c r="I78" t="n">
         <v>14336.15985254141</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K78" t="n">
-        <v>0.03</v>
+        <v>-1.55</v>
       </c>
       <c r="L78" t="n">
-        <v>0.61</v>
+        <v>1.57</v>
       </c>
       <c r="M78" t="n">
         <v>0.01</v>
       </c>
       <c r="N78" t="n">
-        <v>1.3</v>
+        <v>1.83</v>
       </c>
       <c r="O78" t="n">
         <v>1.22</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,25 +5870,25 @@
         <v>4.02</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H79" t="n">
-        <v>14233.8</v>
+        <v>14466.65</v>
       </c>
       <c r="I79" t="n">
         <v>14332.26215682696</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K79" t="n">
-        <v>0.4</v>
+        <v>-1.23</v>
       </c>
       <c r="L79" t="n">
         <v>1.87</v>
       </c>
       <c r="M79" t="n">
-        <v>1.21</v>
+        <v>1.73</v>
       </c>
       <c r="N79" t="n">
         <v>2.47</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S79" t="b">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>1</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -4980,19 +5939,19 @@
         <v>3.65</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46225.55208333334</v>
+        <v>46226.38541666666</v>
       </c>
       <c r="H80" t="n">
-        <v>14622.1</v>
+        <v>14415.3</v>
       </c>
       <c r="I80" t="n">
         <v>14545.54291290171</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K80" t="n">
-        <v>1.07</v>
+        <v>-0.35</v>
       </c>
       <c r="L80" t="n">
         <v>1.16</v>
@@ -5001,7 +5960,7 @@
         <v>0.68</v>
       </c>
       <c r="N80" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O80" t="n">
         <v>1.34</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>2</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -5037,22 +6008,22 @@
         <v>2.83</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46231.55208333334</v>
+        <v>46232.38541666666</v>
       </c>
       <c r="H81" t="n">
-        <v>14561.6</v>
+        <v>14674.1</v>
       </c>
       <c r="I81" t="n">
         <v>14662.96571586067</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K81" t="n">
-        <v>-1.01</v>
+        <v>-1.8</v>
       </c>
       <c r="L81" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="M81" t="n">
         <v>0.6899999999999999</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>2</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -5094,25 +6077,25 @@
         <v>2.32</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>46266.55208333334</v>
+        <v>46267.38541666666</v>
       </c>
       <c r="H82" t="n">
-        <v>14813.35</v>
+        <v>14623.35</v>
       </c>
       <c r="I82" t="n">
         <v>14807.80861394144</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K82" t="n">
-        <v>0.95</v>
+        <v>-0.35</v>
       </c>
       <c r="L82" t="n">
-        <v>0.57</v>
+        <v>0.83</v>
       </c>
       <c r="M82" t="n">
-        <v>0.29</v>
+        <v>0.66</v>
       </c>
       <c r="N82" t="n">
         <v>1.43</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>2</v>
+      </c>
+      <c r="U82" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -5175,6 +6170,14 @@
       <c r="Q83" t="n">
         <v>74</v>
       </c>
+      <c r="R83" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7277,7 +8280,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.4</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="6">
@@ -7287,7 +8290,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="7">
@@ -7297,7 +8300,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>83.2</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8">
@@ -7307,7 +8310,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -7317,7 +8320,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="10">
@@ -7327,7 +8330,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>41.2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11">
@@ -7337,7 +8340,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12">
@@ -7347,7 +8350,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -7357,7 +8360,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>80.2</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="14">
@@ -7367,7 +8370,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.34</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="15">
@@ -7377,7 +8380,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.41</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="16">
@@ -7387,7 +8390,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.24</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="17">
@@ -7397,7 +8400,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18.47</v>
+        <v>17.46</v>
       </c>
     </row>
     <row r="18">
@@ -7407,7 +8410,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>50.6</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="19">
@@ -7417,7 +8420,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.94</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="20">
@@ -7427,7 +8430,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="21">
@@ -7437,7 +8440,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7.4</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="22">
@@ -7447,7 +8450,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -7457,7 +8460,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -7467,7 +8470,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.71</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="25">
@@ -7477,7 +8480,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.84</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="26">
@@ -7487,7 +8490,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.74</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="27">
@@ -7497,7 +8500,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5.12</v>
+        <v>7.48</v>
       </c>
     </row>
     <row r="28">
@@ -7507,7 +8510,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
